--- a/180/food/2026-01-12-sm.xlsx
+++ b/180/food/2026-01-12-sm.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>12.01.2026</t>
         </is>
       </c>
     </row>
@@ -1151,34 +1151,14 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>Суп картофельный с бобовыми №113</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="n">
-        <v>200</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="G12" s="43" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" s="43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J12" s="44" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="C12" s="26" t="e"/>
+      <c r="D12" s="25" t="e"/>
+      <c r="E12" s="30" t="e"/>
+      <c r="F12" s="30" t="e"/>
+      <c r="G12" s="30" t="e"/>
+      <c r="H12" s="30" t="e"/>
+      <c r="I12" s="30" t="e"/>
+      <c r="J12" s="32" t="e"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="24" t="e"/>
@@ -1188,29 +1168,13 @@
         </is>
       </c>
       <c r="C13" s="26" t="e"/>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>Котлета куриная</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="F13" s="31" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="G13" s="43" t="n">
-        <v>262.7</v>
-      </c>
-      <c r="H13" s="43" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I13" s="43" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="D13" s="25" t="e"/>
+      <c r="E13" s="30" t="e"/>
+      <c r="F13" s="30" t="e"/>
+      <c r="G13" s="30" t="e"/>
+      <c r="H13" s="30" t="e"/>
+      <c r="I13" s="30" t="e"/>
+      <c r="J13" s="32" t="e"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="24" t="e"/>
@@ -1219,34 +1183,14 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>Греча отварная №4.3</t>
-        </is>
-      </c>
-      <c r="E14" s="27" t="n">
-        <v>150</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="G14" s="43" t="n">
-        <v>243.7</v>
-      </c>
-      <c r="H14" s="43" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I14" s="43" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J14" s="44" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="C14" s="26" t="e"/>
+      <c r="D14" s="25" t="e"/>
+      <c r="E14" s="30" t="e"/>
+      <c r="F14" s="30" t="e"/>
+      <c r="G14" s="30" t="e"/>
+      <c r="H14" s="30" t="e"/>
+      <c r="I14" s="30" t="e"/>
+      <c r="J14" s="32" t="e"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="24" t="e"/>
@@ -1255,32 +1199,14 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>Чай с лимоном №459</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>180</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="G15" s="43" t="n">
-        <v>35.1</v>
-      </c>
+      <c r="C15" s="26" t="e"/>
+      <c r="D15" s="25" t="e"/>
+      <c r="E15" s="30" t="e"/>
+      <c r="F15" s="30" t="e"/>
+      <c r="G15" s="30" t="e"/>
       <c r="H15" s="30" t="e"/>
-      <c r="I15" s="43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J15" s="44" t="n">
-        <v>8.6</v>
-      </c>
+      <c r="I15" s="30" t="e"/>
+      <c r="J15" s="32" t="e"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="24" t="e"/>
@@ -1290,29 +1216,13 @@
         </is>
       </c>
       <c r="C16" s="26" t="e"/>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>Хлеб пшеничный</t>
-        </is>
-      </c>
-      <c r="E16" s="27" t="n">
-        <v>80</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>27.73</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>187</v>
-      </c>
-      <c r="H16" s="43" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J16" s="44" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="D16" s="25" t="e"/>
+      <c r="E16" s="30" t="e"/>
+      <c r="F16" s="30" t="e"/>
+      <c r="G16" s="30" t="e"/>
+      <c r="H16" s="30" t="e"/>
+      <c r="I16" s="30" t="e"/>
+      <c r="J16" s="32" t="e"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="24" t="e"/>
